--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0176.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0176.xlsx
@@ -2004,7 +2004,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Cái này không chạy nhanh hơn được à? Hả? Xe của cậu cũng có giới hạn tốc độ à...</t>
+          <t>Cái này không chạy nhanh hơn được à? Hả? Xe của mày cũng có giới hạn tốc độ à...</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Ở đây yên ắng quá. Kể ta nghe một câu chuyện cười đi?</t>
+          <t>Ở đây yên ắng quá. Kể tao nghe một câu chuyện cười đi?</t>
         </is>
       </c>
     </row>
@@ -19294,7 +19294,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Ta đã thấy chúng rồi.</t>
+          <t>Tao đã thấy chúng rồi.</t>
         </is>
       </c>
     </row>
@@ -19749,7 +19749,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Nhưng khi tôi thử chạm vào hình chiếu, chẳng có gì xảy ra cả. Tay tôi xuyên qua thôi. Có lẽ vì tôi không phải Cộng Hưởng Giả.</t>
+          <t>Nhưng khi tôi thử chạm vào hình chiếu, chẳng có gì xảy ra cả. Tay tôi xuyên qua thôi. Có lẽ vì tôi không phải Resonator.</t>
         </is>
       </c>
     </row>
@@ -19879,7 +19879,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Để tôi lo.</t>
+          <t>Để đó cho ta.</t>
         </is>
       </c>
     </row>
@@ -20529,7 +20529,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Rover à, đây là &lt;color=Highlight&gt;Sonance Casket&lt;/color&gt; đấy! Ừm... cậu giữ lấy đi. Tớ có một người quen cũ là &lt;color=Highlight&gt;relic merchant&lt;/color&gt;. Ông ấy biết rất nhiều về những thứ kiểu này. Khi đến Jinzhou, tớ sẽ dẫn cậu đến gặp ông ấy.</t>
+          <t>Rover à, đây là &lt;color=Highlight&gt;Hòm Sonance&lt;/color&gt; đấy! Ừm... cậu giữ lấy đi. Tớ có một người quen cũ là &lt;color=Highlight&gt;thương nhân di vật&lt;/color&gt;. Ông ấy biết rất nhiều về những thứ kiểu này. Khi đến Jinzhou, tớ sẽ dẫn cậu đến gặp ông ấy.</t>
         </is>
       </c>
     </row>
@@ -23259,7 +23259,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Rinascita luôn nằm trong danh sách của chúng ta. Fuling từng nói về việc vẽ hoàng hôn ở Ragunna City và ghé thăm Salotto Mở Air Thư viện.</t>
+          <t>Rinascita luôn nằm trong danh sách của chúng ta. Fuling từng nói về việc vẽ hoàng hôn ở Ragunna City và ghé thăm Salotto Open Air Gallery.</t>
         </is>
       </c>
     </row>
@@ -23324,7 +23324,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Nhưng ta vẫn chưa đủ khỏe để đi xa, nên ta nghĩ có lẽ ngắm cảnh qua tranh ảnh cũng được.</t>
+          <t>Nhưng tao vẫn chưa đủ khỏe để đi xa, nên tao nghĩ có lẽ ngắm cảnh qua tranh ảnh cũng được.</t>
         </is>
       </c>
     </row>
@@ -23454,7 +23454,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Ta có vài cuốn sách ở đây.</t>
+          <t>Tao có vài cuốn sách ở đây.</t>
         </is>
       </c>
     </row>
@@ -24559,7 +24559,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Nó khiến ta nhớ về khoảng thời gian xa xưa, trước khi ta đổ bệnh, khi cậu ấy và ta cùng leo lên ngọn núi cao nhất ở Huanglong.</t>
+          <t>Nó khiến tao nhớ về khoảng thời gian xa xưa, trước khi tao đổ bệnh, khi cậu ấy và tao cùng leo lên ngọn núi cao nhất ở Huanglong.</t>
         </is>
       </c>
     </row>
@@ -26379,7 +26379,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Được chưng cất từ những nguyên liệu thượng hạng của Kim Châu, mọi tinh hoa đều được cô đọng trong một chén... Nhưng kho báu thực sự chính là tấm lòng của mọi người khi sẵn sàng chia sẻ những món ăn quý giá nhất, cậu không nghĩ vậy sao?</t>
+          <t>Được chưng cất từ những nguyên liệu thượng hạng của Jinzhou, mọi tinh hoa đều được cô đọng trong một chén... Nhưng kho báu thực sự chính là tấm lòng của mọi người khi sẵn sàng chia sẻ những món ăn quý giá nhất, cậu không nghĩ vậy sao?</t>
         </is>
       </c>
     </row>
@@ -26509,7 +26509,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Còn tớ, tớ muốn trở thành người có thể bảo vệ mọi sinh mạng ở Kim Châu... kể cả cậu nữa! Tớ cũng muốn bảo vệ cậu đấy! Tớ đã có khoảng thời gian thật tuyệt vời khi ở bên cậu.</t>
+          <t>Còn tớ, tớ muốn trở thành người có thể bảo vệ mọi sinh mạng ở Jinzhou... kể cả cậu nữa! Tớ cũng muốn bảo vệ cậu đấy! Tớ đã có khoảng thời gian thật tuyệt vời khi ở bên cậu.</t>
         </is>
       </c>
     </row>
@@ -26769,7 +26769,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Dù vừa mới ăn xong đĩa thức ăn, nhưng bao tử thứ hai của ta vẫn còn chỗ cho món súp đấy. Rover à, thử không? Dì Panhua, pha cho tụi mình một tô nhé?</t>
+          <t>Dù vừa mới ăn xong đĩa thức ăn, nhưng bao tử thứ hai của ta vẫn còn chỗ cho món súp đấy. Vận Mệnh Giả à, thử không? Dì Panhua, pha cho tụi mình một tô nhé?</t>
         </is>
       </c>
     </row>
@@ -27029,7 +27029,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Không, nghe như ta là nhân viên giao hàng ấy. Mà ta còn cả đống việc khác phải làm, cậu biết mà? Nhưng mà này, ta đến đây để nhờ cậu xem thử công thức này.</t>
+          <t>Không, nghe như tao là nhân viên giao hàng ấy. Mà tao còn cả đống việc khác phải làm, cậu biết mà? Nhưng mà này, tao đến đây để nhờ cậu xem thử công thức này.</t>
         </is>
       </c>
     </row>
@@ -27289,7 +27289,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Nhưng vấn đề ở đây: công thức yêu cầu nước từ Monkvyrid, và một nguyên liệu khác gọi là thìa cán vàng. Thật lòng, ta chả biết gì về hai thứ này cả.</t>
+          <t>Nhưng vấn đề ở đây: công thức yêu cầu nước từ Monkvyrid, và một nguyên liệu khác gọi là thìa cán vàng. Thật lòng, tao chả biết gì về hai thứ này cả.</t>
         </is>
       </c>
     </row>
@@ -27354,7 +27354,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Ta nấu ăn không giỏi, nhưng công thức này trông như món ăn dưỡng sinh hay súp hải sản gì đó vì có nhiều nguyên liệu khác nhau với lượng nhỏ. Cậu thấy sao?</t>
+          <t>Tao nấu ăn không giỏi, nhưng công thức này trông như món ăn dưỡng sinh hay súp hải sản gì đó vì có nhiều nguyên liệu khác nhau với lượng nhỏ. Cậu thấy sao?</t>
         </is>
       </c>
     </row>
@@ -28329,7 +28329,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Này, cầm lấy mấy cái &lt;color=Highlight&gt;casting molds and ores&lt;/color&gt; chưa dùng đến mà Bộ Quân Nhu đưa cho ta. Đây là nguyên liệu để tạo nên vũ khí. Với những thứ này, cậu có thể rèn một món mới.</t>
+          <t>Này, cầm lấy mấy cái &lt;color=Highlight&gt;khuôn đúc và quặng&lt;/color&gt; chưa dùng đến mà Bộ Quân Nhu đưa cho ta. Đây là nguyên liệu để tạo nên vũ khí. Với những thứ này, cậu có thể rèn một món mới.</t>
         </is>
       </c>
     </row>
@@ -28394,7 +28394,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Nếu cậu không thích thứ đang dùng hoặc muốn làm cái khác, cứ đến tìm mình bất cứ lúc nào. Chỉ cần có &lt;color=Highlight&gt;casting molds and ores&lt;/color&gt;, mình sẽ làm cho cậu.</t>
+          <t>Nếu cậu không thích thứ đang dùng hoặc muốn làm cái khác, cứ đến tìm mình bất cứ lúc nào. Chỉ cần có &lt;color=Highlight&gt;khuôn đúc và quặng&lt;/color&gt;, mình sẽ làm cho cậu.</t>
         </is>
       </c>
     </row>
@@ -30279,7 +30279,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Không à? Nếu không thì r?i ?i, ta không có thời gian đùa giỡn với ngươi đâu.</t>
+          <t>Không à? Nếu không thì Rời đi, ta không có thời gian đùa giỡn với ngươi đâu.</t>
         </is>
       </c>
     </row>
